--- a/site/nu_leads.xlsx
+++ b/site/nu_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>North Rankin Nickel Mine</t>
+          <t>Cullaton Mine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>055KNE0083</t>
+          <t>065GSE0016</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium</t>
+          <t>Gold, Silver, As, Copper</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>62.8144</v>
+        <v>61.2669</v>
       </c>
       <c r="W2" t="n">
-        <v>-92.0779</v>
+        <v>-98.4991</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0083</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065GSE0016</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Main Ore Zone</t>
+          <t>Shear Lake</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>048CSE0002</t>
+          <t>065GSE0009</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Cd, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>35</v>
       </c>
       <c r="V3" t="n">
-        <v>73.041</v>
+        <v>61.3057</v>
       </c>
       <c r="W3" t="n">
-        <v>-84.49469999999999</v>
+        <v>-98.5033</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065GSE0009</t>
         </is>
       </c>
     </row>
@@ -714,29 +714,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - K-Baseline Zone</t>
+          <t>Lupin Mine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>048CSE0007</t>
+          <t>076ENW0017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Past Producer Care and Maintnc</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>73.0414</v>
+        <v>65.7647</v>
       </c>
       <c r="W4" t="n">
-        <v>-84.4092</v>
+        <v>-111.225</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0017</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Ocean View Zone</t>
+          <t>Roberts Lake Silver</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>048CSE0004</t>
+          <t>077ASW0004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Silver, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -838,17 +838,17 @@
         <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V5" t="n">
-        <v>73.0463</v>
+        <v>68.1833</v>
       </c>
       <c r="W5" t="n">
-        <v>-84.3865</v>
+        <v>-106.5458</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0004</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Area 14 Zone</t>
+          <t>North Rankin Nickel Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>048CSE0005</t>
+          <t>055KNE0083</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Nickel, Copper, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,17 +910,17 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V6" t="n">
-        <v>73.029</v>
+        <v>62.8144</v>
       </c>
       <c r="W6" t="n">
-        <v>-84.4113</v>
+        <v>-92.0779</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0005</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0083</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Shale Hill Zone</t>
+          <t>Rankin Inlet Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>048CSE0006</t>
+          <t>055KNE0145</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Nickel, Copper, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -982,17 +982,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V7" t="n">
-        <v>73.0478</v>
+        <v>62.8131</v>
       </c>
       <c r="W7" t="n">
-        <v>-84.4639</v>
+        <v>-92.07769999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0006</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0145</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rankin Inlet Mine</t>
+          <t>Nanisivik Mine - K-Baseline Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>055KNE0145</t>
+          <t>048CSE0007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1054,17 +1054,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V8" t="n">
-        <v>62.8131</v>
+        <v>73.0414</v>
       </c>
       <c r="W8" t="n">
-        <v>-92.07769999999999</v>
+        <v>-84.4092</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0145</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0007</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Polaris</t>
+          <t>Nanisivik Mine - Ocean View Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>068HSE0003</t>
+          <t>048CSE0004</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V9" t="n">
-        <v>75.3989</v>
+        <v>73.0463</v>
       </c>
       <c r="W9" t="n">
-        <v>-96.92529999999999</v>
+        <v>-84.3865</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=068HSE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0004</t>
         </is>
       </c>
     </row>
@@ -1146,29 +1146,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cullaton Mine</t>
+          <t>steve test</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>065GSE0016</t>
+          <t>016LSE0001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Gold, Silver, As, Copper</t>
-        </is>
-      </c>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Minor Past Producer Renewed Exploration</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1198,17 +1194,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V10" t="n">
-        <v>61.2669</v>
+        <v>62.2542</v>
       </c>
       <c r="W10" t="n">
-        <v>-98.4991</v>
+        <v>-62.2542</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065GSE0016</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=016LSE0001</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1214,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Roberts Lake Silver</t>
+          <t>Polaris</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>077ASW0004</t>
+          <t>068HSE0003</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1270,17 +1266,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V11" t="n">
-        <v>68.1833</v>
+        <v>75.3989</v>
       </c>
       <c r="W11" t="n">
-        <v>-106.5458</v>
+        <v>-96.92529999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=068HSE0003</t>
         </is>
       </c>
     </row>
@@ -1290,29 +1286,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lupin Mine</t>
+          <t>Nanisivik Mine - Area 14 Zone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>076ENW0017</t>
+          <t>048CSE0005</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producer Care and Maintnc</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1342,17 +1338,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>65.7647</v>
+        <v>73.029</v>
       </c>
       <c r="W12" t="n">
-        <v>-111.225</v>
+        <v>-84.4113</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0017</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0005</t>
         </is>
       </c>
     </row>
@@ -1362,24 +1358,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shear Lake</t>
+          <t>Nanisivik Mine - Shale Hill Zone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>065GSE0009</t>
+          <t>048CSE0006</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1414,17 +1410,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V13" t="n">
-        <v>61.3057</v>
+        <v>73.0478</v>
       </c>
       <c r="W13" t="n">
-        <v>-98.5033</v>
+        <v>-84.4639</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065GSE0009</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0006</t>
         </is>
       </c>
     </row>
@@ -1434,25 +1430,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>steve test</t>
+          <t>Nanisivik Mine - Main Ore Zone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>016LSE0001</t>
+          <t>048CSE0002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Silver, Cd, Copper</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Minor Past Producer Renewed Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1485,14 +1485,14 @@
         <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>62.2542</v>
+        <v>73.041</v>
       </c>
       <c r="W14" t="n">
-        <v>-62.2542</v>
+        <v>-84.49469999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=016LSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0002</t>
         </is>
       </c>
     </row>

--- a/site/nu_leads.xlsx
+++ b/site/nu_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X108"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,10 +616,10 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U2" t="n">
         <v>35</v>
@@ -688,10 +688,10 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U3" t="n">
         <v>35</v>
@@ -714,29 +714,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lupin Mine</t>
+          <t>steve test</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>076ENW0017</t>
+          <t>016LSE0001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producer Care and Maintnc</t>
+          <t>Minor Past Producer Renewed Exploration</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -766,17 +762,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V4" t="n">
-        <v>65.7647</v>
+        <v>62.2542</v>
       </c>
       <c r="W4" t="n">
-        <v>-111.225</v>
+        <v>-62.2542</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0017</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=016LSE0001</t>
         </is>
       </c>
     </row>
@@ -786,24 +782,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Roberts Lake Silver</t>
+          <t>Polaris</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>077ASW0004</t>
+          <t>068HSE0003</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -838,17 +834,17 @@
         <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="V5" t="n">
-        <v>68.1833</v>
+        <v>75.3989</v>
       </c>
       <c r="W5" t="n">
-        <v>-106.5458</v>
+        <v>-96.92529999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=068HSE0003</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>North Rankin Nickel Mine</t>
+          <t>Eqe Bay Iron Zone #4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>055KNE0083</t>
+          <t>037CNE0006</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -910,17 +906,17 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="V6" t="n">
-        <v>62.8144</v>
+        <v>69.67400000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-92.0779</v>
+        <v>-76.8459</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0083</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0006</t>
         </is>
       </c>
     </row>
@@ -930,29 +926,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rankin Inlet Mine</t>
+          <t>Mary River - No. 3a Deposit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>055KNE0145</t>
+          <t>037GSW0009</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -982,17 +978,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="V7" t="n">
-        <v>62.8131</v>
+        <v>71.3188</v>
       </c>
       <c r="W7" t="n">
-        <v>-92.07769999999999</v>
+        <v>-79.08110000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0145</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0009</t>
         </is>
       </c>
     </row>
@@ -1002,29 +998,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - K-Baseline Zone</t>
+          <t>Eqe Bay Iron Zone #5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>048CSE0007</t>
+          <t>037CNE0007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1054,17 +1050,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V8" t="n">
-        <v>73.0414</v>
+        <v>69.66670000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>-84.4092</v>
+        <v>-76.875</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0007</t>
         </is>
       </c>
     </row>
@@ -1074,29 +1070,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Ocean View Zone</t>
+          <t>Eqe Bay Iron Zone #6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>048CSE0004</t>
+          <t>037CNE0008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1126,17 +1122,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V9" t="n">
-        <v>73.0463</v>
+        <v>69.66589999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-84.3865</v>
+        <v>-76.82510000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0008</t>
         </is>
       </c>
     </row>
@@ -1146,25 +1142,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>steve test</t>
+          <t>Eqe Bay Iron Zone #7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>016LSE0001</t>
+          <t>037CNE0009</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Minor Past Producer Renewed Exploration</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1194,17 +1194,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V10" t="n">
-        <v>62.2542</v>
+        <v>69.67659999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-62.2542</v>
+        <v>-76.92449999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=016LSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0009</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1214,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Polaris</t>
+          <t>Eqe Bay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>068HSE0003</t>
+          <t>037CNE0010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1266,17 +1266,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V11" t="n">
-        <v>75.3989</v>
+        <v>69.6733</v>
       </c>
       <c r="W11" t="n">
-        <v>-96.92529999999999</v>
+        <v>-76.8056</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=068HSE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0010</t>
         </is>
       </c>
     </row>
@@ -1286,29 +1286,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Area 14 Zone</t>
+          <t>Mary River - No. 1 Deposit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>048CSE0005</t>
+          <t>037GSW0002</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1338,17 +1338,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V12" t="n">
-        <v>73.029</v>
+        <v>71.32380000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>-84.4113</v>
+        <v>-79.24160000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0005</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0002</t>
         </is>
       </c>
     </row>
@@ -1358,29 +1358,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Shale Hill Zone</t>
+          <t>Mary River - No. 2 Deposit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>048CSE0006</t>
+          <t>037GSW0007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1410,17 +1410,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V13" t="n">
-        <v>73.0478</v>
+        <v>71.32250000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-84.4639</v>
+        <v>-79.1327</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0006</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0007</t>
         </is>
       </c>
     </row>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nanisivik Mine - Main Ore Zone</t>
+          <t>Mary River - No. 3 Deposit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>048CSE0002</t>
+          <t>037GSW0008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Cd, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Advanced Exploration</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1482,17 +1482,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="V14" t="n">
-        <v>73.041</v>
+        <v>71.3168</v>
       </c>
       <c r="W14" t="n">
-        <v>-84.49469999999999</v>
+        <v>-79.12869999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0008</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #4</t>
+          <t>Borealis - 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>037CNE0006</t>
+          <t>047BSE0001</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1557,14 +1557,14 @@
         <v>19</v>
       </c>
       <c r="V15" t="n">
-        <v>69.67400000000001</v>
+        <v>68.21850000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.8459</v>
+        <v>-85.4945</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0006</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0001</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mary River - No. 3a Deposit</t>
+          <t>Area 'D'</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>037GSW0009</t>
+          <t>047ASW0009</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1629,14 +1629,14 @@
         <v>19</v>
       </c>
       <c r="V16" t="n">
-        <v>71.3188</v>
+        <v>68.3702</v>
       </c>
       <c r="W16" t="n">
-        <v>-79.08110000000001</v>
+        <v>-82.97620000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0009</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0009</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #5</t>
+          <t>Area 'E'</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>037CNE0007</t>
+          <t>047ASW0007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1701,14 +1701,14 @@
         <v>19</v>
       </c>
       <c r="V17" t="n">
-        <v>69.66670000000001</v>
+        <v>68.1631</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.875</v>
+        <v>-83.38849999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0007</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #6</t>
+          <t>Area 'B'</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>037CNE0008</t>
+          <t>047ASW0004</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1773,14 +1773,14 @@
         <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>69.66589999999999</v>
+        <v>68.46120000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.82510000000001</v>
+        <v>-82.7294</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0008</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0004</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #7</t>
+          <t>Area 'A' / Adler</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>037CNE0009</t>
+          <t>047ASW0001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1845,14 +1845,14 @@
         <v>19</v>
       </c>
       <c r="V19" t="n">
-        <v>69.67659999999999</v>
+        <v>68.47150000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.92449999999999</v>
+        <v>-82.7221</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0009</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0001</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eqe Bay</t>
+          <t>Borealis - 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>037CNE0010</t>
+          <t>047BSE0002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1917,14 +1917,14 @@
         <v>19</v>
       </c>
       <c r="V20" t="n">
-        <v>69.6733</v>
+        <v>68.2056</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.8056</v>
+        <v>-85.4928</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0010</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0002</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mary River - No. 1 Deposit</t>
+          <t>Borealis - 5 Southern Zone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>037GSW0002</t>
+          <t>047BSE0027</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1989,14 +1989,14 @@
         <v>19</v>
       </c>
       <c r="V21" t="n">
-        <v>71.32380000000001</v>
+        <v>68.3648</v>
       </c>
       <c r="W21" t="n">
-        <v>-79.24160000000001</v>
+        <v>-85.3108</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0027</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mary River - No. 2 Deposit</t>
+          <t>Borealis - 5 Northern Zone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>037GSW0007</t>
+          <t>047BSE0026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2061,14 +2061,14 @@
         <v>19</v>
       </c>
       <c r="V22" t="n">
-        <v>71.32250000000001</v>
+        <v>68.3794</v>
       </c>
       <c r="W22" t="n">
-        <v>-79.1327</v>
+        <v>-85.26819999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0026</t>
         </is>
       </c>
     </row>
@@ -2078,26 +2078,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mary River - No. 3 Deposit</t>
+          <t>Borealis - 3 East Limb</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>037GSW0008</t>
+          <t>047BSE0025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Advanced Exploration</t>
@@ -2133,14 +2129,14 @@
         <v>19</v>
       </c>
       <c r="V23" t="n">
-        <v>71.3168</v>
+        <v>68.18899999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-79.12869999999999</v>
+        <v>-85.4982</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0008</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0025</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2146,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Borealis - 1</t>
+          <t>Borealis - 1 North Extension</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>047BSE0001</t>
+          <t>047BSE0024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2205,14 +2201,14 @@
         <v>19</v>
       </c>
       <c r="V24" t="n">
-        <v>68.21850000000001</v>
+        <v>68.2272</v>
       </c>
       <c r="W24" t="n">
-        <v>-85.4945</v>
+        <v>-85.4879</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0024</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2218,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Area 'D'</t>
+          <t>Borealis - 5 Central Zone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>047ASW0009</t>
+          <t>047BSE0005</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2277,14 +2273,14 @@
         <v>19</v>
       </c>
       <c r="V25" t="n">
-        <v>68.3702</v>
+        <v>68.37090000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>-82.97620000000001</v>
+        <v>-85.28060000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0009</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0005</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2290,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Area 'C'</t>
+          <t>Borealis - 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>047ASW0008</t>
+          <t>047BSE0004</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2349,14 +2345,14 @@
         <v>19</v>
       </c>
       <c r="V26" t="n">
-        <v>68.4328</v>
+        <v>68.2987</v>
       </c>
       <c r="W26" t="n">
-        <v>-82.78619999999999</v>
+        <v>-85.28279999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0008</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0004</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2362,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Area 'E'</t>
+          <t>Borealis - 3 West Limb</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>047ASW0007</t>
+          <t>047BSE0003</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2421,14 +2417,14 @@
         <v>19</v>
       </c>
       <c r="V27" t="n">
-        <v>68.1631</v>
+        <v>68.1915</v>
       </c>
       <c r="W27" t="n">
-        <v>-83.38849999999999</v>
+        <v>-85.50920000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0003</t>
         </is>
       </c>
     </row>
@@ -2438,24 +2434,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Area 'B'</t>
+          <t>Turquetil Lake Northwest</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>047ASW0004</t>
+          <t>055ENW0007</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2484,23 +2480,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U28" t="n">
         <v>19</v>
       </c>
       <c r="V28" t="n">
-        <v>68.46120000000001</v>
+        <v>61.98</v>
       </c>
       <c r="W28" t="n">
-        <v>-82.7294</v>
+        <v>-95.9267</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055ENW0007</t>
         </is>
       </c>
     </row>
@@ -2510,24 +2506,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Area 'A' / Adler</t>
+          <t>Fat Lake</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>047ASW0001</t>
+          <t>055KSW0041</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold, Copper, Lead, As, Zinc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2565,14 +2561,14 @@
         <v>19</v>
       </c>
       <c r="V29" t="n">
-        <v>68.47150000000001</v>
+        <v>62.1201</v>
       </c>
       <c r="W29" t="n">
-        <v>-82.7221</v>
+        <v>-93.8631</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KSW0041</t>
         </is>
       </c>
     </row>
@@ -2582,24 +2578,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mary River - No. 4 Deposit</t>
+          <t>Cache Zone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>037GSW0010</t>
+          <t>055LSE0045</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2628,23 +2624,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>19</v>
       </c>
       <c r="V30" t="n">
-        <v>71.4611</v>
+        <v>62.3675</v>
       </c>
       <c r="W30" t="n">
-        <v>-79.8638</v>
+        <v>-94.6288</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0010</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0045</t>
         </is>
       </c>
     </row>
@@ -2654,24 +2650,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Borealis - 2</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>047BSE0002</t>
+          <t>055LSE0254</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Uranium, fluorspar</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2709,14 +2705,14 @@
         <v>19</v>
       </c>
       <c r="V31" t="n">
-        <v>68.2056</v>
+        <v>62.3253</v>
       </c>
       <c r="W31" t="n">
-        <v>-85.4928</v>
+        <v>-94.65009999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0254</t>
         </is>
       </c>
     </row>
@@ -2726,24 +2722,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Borealis - 5 Southern Zone</t>
+          <t>Spi Lake</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>047BSE0027</t>
+          <t>055LSW0133</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Copper, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2781,14 +2777,14 @@
         <v>19</v>
       </c>
       <c r="V32" t="n">
-        <v>68.3648</v>
+        <v>62.0699</v>
       </c>
       <c r="W32" t="n">
-        <v>-85.3108</v>
+        <v>-95.8784</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0027</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSW0133</t>
         </is>
       </c>
     </row>
@@ -2798,12 +2794,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Borealis - 5 Northern Zone</t>
+          <t>Maltby Lake Iron Deposit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>047BSE0026</t>
+          <t>036CNW0001</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2853,14 +2849,14 @@
         <v>19</v>
       </c>
       <c r="V33" t="n">
-        <v>68.3794</v>
+        <v>64.91670000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>-85.26819999999999</v>
+        <v>-77.9333</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0026</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=036CNW0001</t>
         </is>
       </c>
     </row>
@@ -2870,22 +2866,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Borealis - 3 East Limb</t>
+          <t>Eqe Bay Iron Zone #1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>047BSE0025</t>
+          <t>037CNE0001</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Advanced Exploration</t>
@@ -2921,14 +2921,14 @@
         <v>19</v>
       </c>
       <c r="V34" t="n">
-        <v>68.18899999999999</v>
+        <v>69.68989999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>-85.4982</v>
+        <v>-76.7471</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0025</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0001</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Borealis - 1 North Extension</t>
+          <t>Eqe Bay Iron Zone #1A</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>047BSE0024</t>
+          <t>037CNE0002</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2993,14 +2993,14 @@
         <v>19</v>
       </c>
       <c r="V35" t="n">
-        <v>68.2272</v>
+        <v>69.71120000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>-85.4879</v>
+        <v>-76.6835</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0024</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0002</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Borealis - 5 Central Zone</t>
+          <t>Eqe Bay Iron Zone #2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>047BSE0005</t>
+          <t>037CNE0003</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3065,14 +3065,14 @@
         <v>19</v>
       </c>
       <c r="V36" t="n">
-        <v>68.37090000000001</v>
+        <v>69.6797</v>
       </c>
       <c r="W36" t="n">
-        <v>-85.28060000000001</v>
+        <v>-76.8171</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0005</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0003</t>
         </is>
       </c>
     </row>
@@ -3082,24 +3082,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nanisivik Mines - North Pyrite Zone</t>
+          <t>Eqe Bay Iron Zone #3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>048CSE0012</t>
+          <t>037CNE0004</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3137,14 +3137,14 @@
         <v>19</v>
       </c>
       <c r="V37" t="n">
-        <v>73.05370000000001</v>
+        <v>69.6778</v>
       </c>
       <c r="W37" t="n">
-        <v>-84.4376</v>
+        <v>-76.8</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0012</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0004</t>
         </is>
       </c>
     </row>
@@ -3154,24 +3154,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Borealis - 4</t>
+          <t>Rochon Lake</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>047BSE0004</t>
+          <t>065CNW0012</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3209,14 +3209,14 @@
         <v>19</v>
       </c>
       <c r="V38" t="n">
-        <v>68.2987</v>
+        <v>60.8211</v>
       </c>
       <c r="W38" t="n">
-        <v>-85.28279999999999</v>
+        <v>-101.9109</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065CNW0012</t>
         </is>
       </c>
     </row>
@@ -3226,24 +3226,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Borealis - 3 West Limb</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>047BSE0003</t>
+          <t>058CSW0004</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Diam</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3281,14 +3281,14 @@
         <v>19</v>
       </c>
       <c r="V39" t="n">
-        <v>68.1915</v>
+        <v>73.4628</v>
       </c>
       <c r="W39" t="n">
-        <v>-85.50920000000001</v>
+        <v>-92.3297</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0004</t>
         </is>
       </c>
     </row>
@@ -3298,24 +3298,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Turquetil Lake Main Zone</t>
+          <t>Batty</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>055ENW0008</t>
+          <t>058CSW0003</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, As, Copper, Zinc</t>
+          <t>Diam</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3353,14 +3353,14 @@
         <v>19</v>
       </c>
       <c r="V40" t="n">
-        <v>61.9718</v>
+        <v>73.34690000000001</v>
       </c>
       <c r="W40" t="n">
-        <v>-95.94070000000001</v>
+        <v>-92.015</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055ENW0008</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0003</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Turquetil Lake Northwest</t>
+          <t>Lowo Lake</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>055ENW0007</t>
+          <t>065HSW0013</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, As</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3425,14 +3425,14 @@
         <v>19</v>
       </c>
       <c r="V41" t="n">
-        <v>61.98</v>
+        <v>61.0527</v>
       </c>
       <c r="W41" t="n">
-        <v>-95.9267</v>
+        <v>-97.8574</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055ENW0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HSW0013</t>
         </is>
       </c>
     </row>
@@ -3442,24 +3442,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Meliadine East</t>
+          <t>Outlet Bay</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>055JNW0001</t>
+          <t>065NSE0001</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold, As, Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3497,14 +3497,14 @@
         <v>19</v>
       </c>
       <c r="V42" t="n">
-        <v>62.9602</v>
+        <v>63.3503</v>
       </c>
       <c r="W42" t="n">
-        <v>-91.9315</v>
+        <v>-100.5005</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055JNW0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065NSE0001</t>
         </is>
       </c>
     </row>
@@ -3514,24 +3514,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fat Lake</t>
+          <t>Kiggavik East Zone</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>055KSW0041</t>
+          <t>066ASW0017</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, As, Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3560,23 +3560,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T43" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U43" t="n">
         <v>19</v>
       </c>
       <c r="V43" t="n">
-        <v>62.1201</v>
+        <v>64.4461</v>
       </c>
       <c r="W43" t="n">
-        <v>-93.8631</v>
+        <v>-97.6181</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KSW0041</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0017</t>
         </is>
       </c>
     </row>
@@ -3586,24 +3586,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cache Zone</t>
+          <t>Bong Grid</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>055LSE0045</t>
+          <t>066ASW0018</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3641,14 +3641,14 @@
         <v>19</v>
       </c>
       <c r="V44" t="n">
-        <v>62.3675</v>
+        <v>64.4158</v>
       </c>
       <c r="W44" t="n">
-        <v>-94.6288</v>
+        <v>-97.70310000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0045</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0018</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Sleek Grid</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>055LSE0254</t>
+          <t>066ASW0020</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uranium, fluorspar</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3704,23 +3704,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T45" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U45" t="n">
         <v>19</v>
       </c>
       <c r="V45" t="n">
-        <v>62.3253</v>
+        <v>64.36279999999999</v>
       </c>
       <c r="W45" t="n">
-        <v>-94.65009999999999</v>
+        <v>-97.8369</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0254</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0020</t>
         </is>
       </c>
     </row>
@@ -3730,24 +3730,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Spi Lake</t>
+          <t>Granite Grid</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>055LSW0133</t>
+          <t>066ASW0019</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Gold, Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3776,23 +3776,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T46" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U46" t="n">
         <v>19</v>
       </c>
       <c r="V46" t="n">
-        <v>62.0699</v>
+        <v>64.4297</v>
       </c>
       <c r="W46" t="n">
-        <v>-95.8784</v>
+        <v>-97.7792</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSW0133</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0019</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shane Lake Project - Ms Claims</t>
+          <t>Andrew Lake Deposit</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>055MNW0038</t>
+          <t>066ASW0022</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3857,14 +3857,14 @@
         <v>19</v>
       </c>
       <c r="V47" t="n">
-        <v>63.8337</v>
+        <v>64.3344</v>
       </c>
       <c r="W47" t="n">
-        <v>-95.0335</v>
+        <v>-97.8961</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055MNW0038</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0022</t>
         </is>
       </c>
     </row>
@@ -3874,24 +3874,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Meliadine West</t>
+          <t>End Grid</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>055NSE0001</t>
+          <t>066ASW0021</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold, As, Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3929,14 +3929,14 @@
         <v>19</v>
       </c>
       <c r="V48" t="n">
-        <v>63.0226</v>
+        <v>64.3456</v>
       </c>
       <c r="W48" t="n">
-        <v>-92.20569999999999</v>
+        <v>-97.86499999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055NSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0021</t>
         </is>
       </c>
     </row>
@@ -3946,12 +3946,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wolf Main</t>
+          <t>Vault</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>055NSE0003</t>
+          <t>066HSE0012</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold, As, Lead</t>
+          <t>Gold, Copper, As, Zinc, Lead</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4001,14 +4001,14 @@
         <v>19</v>
       </c>
       <c r="V49" t="n">
-        <v>63.0303</v>
+        <v>65.0763</v>
       </c>
       <c r="W49" t="n">
-        <v>-92.29989999999999</v>
+        <v>-96.0031</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055NSE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0012</t>
         </is>
       </c>
     </row>
@@ -4018,24 +4018,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maltby Lake Iron Deposit</t>
+          <t>Third Portage</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>036CNW0001</t>
+          <t>066HSE0015</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold, Copper, As</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4073,14 +4073,14 @@
         <v>19</v>
       </c>
       <c r="V50" t="n">
-        <v>64.91670000000001</v>
+        <v>65.01739999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>-77.9333</v>
+        <v>-96.04810000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=036CNW0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0015</t>
         </is>
       </c>
     </row>
@@ -4090,24 +4090,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #1</t>
+          <t>Goose Island</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>037CNE0001</t>
+          <t>066HSE0017</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold, Copper, As</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4145,14 +4145,14 @@
         <v>19</v>
       </c>
       <c r="V51" t="n">
-        <v>69.68989999999999</v>
+        <v>65.0057</v>
       </c>
       <c r="W51" t="n">
-        <v>-76.7471</v>
+        <v>-96.0556</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0017</t>
         </is>
       </c>
     </row>
@@ -4162,24 +4162,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #1A</t>
+          <t>North Portage</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>037CNE0002</t>
+          <t>066HSE0016</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold, Copper, As</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4217,14 +4217,14 @@
         <v>19</v>
       </c>
       <c r="V52" t="n">
-        <v>69.71120000000001</v>
+        <v>65.0273</v>
       </c>
       <c r="W52" t="n">
-        <v>-76.6835</v>
+        <v>-96.0487</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0016</t>
         </is>
       </c>
     </row>
@@ -4234,24 +4234,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #2</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>037CNE0003</t>
+          <t>066HSE0023</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold, As, Copper</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4280,23 +4280,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U53" t="n">
         <v>19</v>
       </c>
       <c r="V53" t="n">
-        <v>69.6797</v>
+        <v>65.15219999999999</v>
       </c>
       <c r="W53" t="n">
-        <v>-76.8171</v>
+        <v>-96.0887</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0023</t>
         </is>
       </c>
     </row>
@@ -4306,24 +4306,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #3</t>
+          <t>Bay Zone</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>037CNE0004</t>
+          <t>066HSE0024</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold, Copper, As</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4361,14 +4361,14 @@
         <v>19</v>
       </c>
       <c r="V54" t="n">
-        <v>69.6778</v>
+        <v>65.01479999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>-76.8</v>
+        <v>-96.0534</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0024</t>
         </is>
       </c>
     </row>
@@ -4378,24 +4378,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rochon Lake</t>
+          <t>Kiggavik Centre Zone</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>065CNW0012</t>
+          <t>066ASW0016</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4424,23 +4424,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U55" t="n">
         <v>19</v>
       </c>
       <c r="V55" t="n">
-        <v>60.8211</v>
+        <v>64.4453</v>
       </c>
       <c r="W55" t="n">
-        <v>-101.9109</v>
+        <v>-97.6319</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065CNW0012</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0016</t>
         </is>
       </c>
     </row>
@@ -4450,24 +4450,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>058CSW0004</t>
+          <t>076ENE0001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Diam</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4505,14 +4505,14 @@
         <v>19</v>
       </c>
       <c r="V56" t="n">
-        <v>73.4628</v>
+        <v>65.6164</v>
       </c>
       <c r="W56" t="n">
-        <v>-92.3297</v>
+        <v>-110.7828</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0001</t>
         </is>
       </c>
     </row>
@@ -4522,24 +4522,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Batty</t>
+          <t>Cannu Zone</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>058CSW0003</t>
+          <t>066HSE0035</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Diam</t>
+          <t>Gold, Copper, As</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4577,14 +4577,14 @@
         <v>19</v>
       </c>
       <c r="V57" t="n">
-        <v>73.34690000000001</v>
+        <v>65.0324</v>
       </c>
       <c r="W57" t="n">
-        <v>-92.015</v>
+        <v>-96.0479</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0035</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Three Bluffs</t>
+          <t>Jon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>056JNW0007</t>
+          <t>076ENE0002</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold, As, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4649,14 +4649,14 @@
         <v>19</v>
       </c>
       <c r="V58" t="n">
-        <v>66.6497</v>
+        <v>65.5814</v>
       </c>
       <c r="W58" t="n">
-        <v>-91.4093</v>
+        <v>-110.9686</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=056JNW0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0002</t>
         </is>
       </c>
     </row>
@@ -4666,24 +4666,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pump</t>
+          <t>Jericho North</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>055NSE0004</t>
+          <t>076ENW0031</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, As</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4712,23 +4712,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U59" t="n">
         <v>19</v>
       </c>
       <c r="V59" t="n">
-        <v>63.009</v>
+        <v>65.9992</v>
       </c>
       <c r="W59" t="n">
-        <v>-92.2201</v>
+        <v>-111.4777</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055NSE0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0031</t>
         </is>
       </c>
     </row>
@@ -4738,24 +4738,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ferguson Lake</t>
+          <t>Hackett River</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>065INE0001</t>
+          <t>076FNE0001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Palladium</t>
+          <t>Zinc, Lead, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4793,14 +4793,14 @@
         <v>19</v>
       </c>
       <c r="V60" t="n">
-        <v>62.8733</v>
+        <v>65.91719999999999</v>
       </c>
       <c r="W60" t="n">
-        <v>-96.8331</v>
+        <v>-108.3631</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076FNE0001</t>
         </is>
       </c>
     </row>
@@ -4810,24 +4810,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lowo Lake</t>
+          <t>Gondor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>065HSW0013</t>
+          <t>076ENW0005</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold, As</t>
+          <t>Zinc, Silver, Copper, Lead, Gold</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4865,14 +4865,14 @@
         <v>19</v>
       </c>
       <c r="V61" t="n">
-        <v>61.0527</v>
+        <v>65.5628</v>
       </c>
       <c r="W61" t="n">
-        <v>-97.8574</v>
+        <v>-111.7969</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HSW0013</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0005</t>
         </is>
       </c>
     </row>
@@ -4882,12 +4882,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Heninga Lake - Eastern Zone</t>
+          <t>Musk</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>065HNE0023</t>
+          <t>076GSW0001</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Zinc, Lead, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4937,14 +4937,14 @@
         <v>19</v>
       </c>
       <c r="V62" t="n">
-        <v>61.7756</v>
+        <v>65.3231</v>
       </c>
       <c r="W62" t="n">
-        <v>-96.1996</v>
+        <v>-107.6208</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HNE0023</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076GSW0001</t>
         </is>
       </c>
     </row>
@@ -4954,24 +4954,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>M Zone</t>
+          <t>Gumbo Lake Ilmenite</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>065INE0005</t>
+          <t>076LSW0008</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Platinum, Palladium</t>
+          <t>Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5009,14 +5009,14 @@
         <v>19</v>
       </c>
       <c r="V63" t="n">
-        <v>62.8742</v>
+        <v>66.3167</v>
       </c>
       <c r="W63" t="n">
-        <v>-96.80110000000001</v>
+        <v>-111.1944</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0005</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076LSW0008</t>
         </is>
       </c>
     </row>
@@ -5026,22 +5026,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>M Zone</t>
+          <t>North Central Vein</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>065ISE0011</t>
+          <t>076MNW0084</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Advanced Exploration</t>
@@ -5077,14 +5081,14 @@
         <v>19</v>
       </c>
       <c r="V64" t="n">
-        <v>62.8742</v>
+        <v>67.7175</v>
       </c>
       <c r="W64" t="n">
-        <v>-96.78440000000001</v>
+        <v>-111.3711</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065ISE0011</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0084</t>
         </is>
       </c>
     </row>
@@ -5094,24 +5098,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nip, Rev (noranda Expln.)</t>
+          <t>Fred Vein</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>065JNE0019</t>
+          <t>076MNW0085</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Uranium, Copper, Silver, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5149,14 +5153,14 @@
         <v>19</v>
       </c>
       <c r="V65" t="n">
-        <v>62.5303</v>
+        <v>67.71810000000001</v>
       </c>
       <c r="W65" t="n">
-        <v>-98.7829</v>
+        <v>-111.3583</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065JNE0019</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0085</t>
         </is>
       </c>
     </row>
@@ -5166,24 +5170,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rib &amp; Fst (Noranda Expln.)</t>
+          <t>High Lake AB Zone</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>065JNW0006</t>
+          <t>076MSE0053</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5212,23 +5216,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U66" t="n">
         <v>19</v>
       </c>
       <c r="V66" t="n">
-        <v>62.5331</v>
+        <v>67.3814</v>
       </c>
       <c r="W66" t="n">
-        <v>-99.0907</v>
+        <v>-110.85</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065JNW0006</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0053</t>
         </is>
       </c>
     </row>
@@ -5238,24 +5242,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Outlet Bay</t>
+          <t>High Lake D Zone</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>065NSE0001</t>
+          <t>076MSE0054</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5284,23 +5288,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U67" t="n">
         <v>19</v>
       </c>
       <c r="V67" t="n">
-        <v>63.3503</v>
+        <v>67.3758</v>
       </c>
       <c r="W67" t="n">
-        <v>-100.5005</v>
+        <v>-110.8436</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065NSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0054</t>
         </is>
       </c>
     </row>
@@ -5310,24 +5314,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nutarawit Lake</t>
+          <t>Izok Lake</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>065OSE0003</t>
+          <t>086HNE0087</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5365,14 +5369,14 @@
         <v>19</v>
       </c>
       <c r="V68" t="n">
-        <v>63.0786</v>
+        <v>65.6311</v>
       </c>
       <c r="W68" t="n">
-        <v>-98.352</v>
+        <v>-112.7989</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065OSE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086HNE0087</t>
         </is>
       </c>
     </row>
@@ -5382,24 +5386,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ferguson Lake</t>
+          <t>Takijuq H-41</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>065INE0002</t>
+          <t>086ISE0001</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt, Platinum</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5437,14 +5441,14 @@
         <v>19</v>
       </c>
       <c r="V69" t="n">
-        <v>62.8667</v>
+        <v>66.0342</v>
       </c>
       <c r="W69" t="n">
-        <v>-96.8417</v>
+        <v>-112.7094</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0001</t>
         </is>
       </c>
     </row>
@@ -5454,24 +5458,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Heninga Lake - West Zone</t>
+          <t>Takijuq H-10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>065HNE0042</t>
+          <t>086ISE0002</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Zinc, Lead, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5509,14 +5513,14 @@
         <v>19</v>
       </c>
       <c r="V70" t="n">
-        <v>61.7733</v>
+        <v>66.06</v>
       </c>
       <c r="W70" t="n">
-        <v>-96.21129999999999</v>
+        <v>-112.7536</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HNE0042</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0002</t>
         </is>
       </c>
     </row>
@@ -5526,24 +5530,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kiggavik East Zone</t>
+          <t>Coronation Northwest Zone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>066ASW0017</t>
+          <t>086NSE0014</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5581,14 +5585,14 @@
         <v>19</v>
       </c>
       <c r="V71" t="n">
-        <v>64.4461</v>
+        <v>67.3347</v>
       </c>
       <c r="W71" t="n">
-        <v>-97.6181</v>
+        <v>-116.45</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0017</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0014</t>
         </is>
       </c>
     </row>
@@ -5598,24 +5602,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bong Grid</t>
+          <t>Wreck Lake</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>066ASW0018</t>
+          <t>086NSE0121</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5653,2604 +5657,12 @@
         <v>19</v>
       </c>
       <c r="V72" t="n">
-        <v>64.4158</v>
+        <v>67.41</v>
       </c>
       <c r="W72" t="n">
-        <v>-97.70310000000001</v>
+        <v>-116.4119</v>
       </c>
       <c r="X72" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0018</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Sleek Grid</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>066ASW0020</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>13</v>
-      </c>
-      <c r="T73" t="n">
-        <v>325</v>
-      </c>
-      <c r="U73" t="n">
-        <v>19</v>
-      </c>
-      <c r="V73" t="n">
-        <v>64.36279999999999</v>
-      </c>
-      <c r="W73" t="n">
-        <v>-97.8369</v>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0020</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Granite Grid</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>066ASW0019</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="n">
-        <v>13</v>
-      </c>
-      <c r="T74" t="n">
-        <v>325</v>
-      </c>
-      <c r="U74" t="n">
-        <v>19</v>
-      </c>
-      <c r="V74" t="n">
-        <v>64.4297</v>
-      </c>
-      <c r="W74" t="n">
-        <v>-97.7792</v>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0019</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Andrew Lake Deposit</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>066ASW0022</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="n">
-        <v>13</v>
-      </c>
-      <c r="T75" t="n">
-        <v>325</v>
-      </c>
-      <c r="U75" t="n">
-        <v>19</v>
-      </c>
-      <c r="V75" t="n">
-        <v>64.3344</v>
-      </c>
-      <c r="W75" t="n">
-        <v>-97.8961</v>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0022</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Naujatuuk Lake</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>066GSE0002</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Uranium, Iron</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>13</v>
-      </c>
-      <c r="T76" t="n">
-        <v>325</v>
-      </c>
-      <c r="U76" t="n">
-        <v>19</v>
-      </c>
-      <c r="V76" t="n">
-        <v>65.2004</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-98.9171</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066GSE0002</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>End Grid</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>066ASW0021</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>13</v>
-      </c>
-      <c r="T77" t="n">
-        <v>325</v>
-      </c>
-      <c r="U77" t="n">
-        <v>19</v>
-      </c>
-      <c r="V77" t="n">
-        <v>64.3456</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-97.86499999999999</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0021</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>066HSE0023</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Gold, As, Copper</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>13</v>
-      </c>
-      <c r="T78" t="n">
-        <v>325</v>
-      </c>
-      <c r="U78" t="n">
-        <v>19</v>
-      </c>
-      <c r="V78" t="n">
-        <v>65.15219999999999</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-96.0887</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0023</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Kiggavik Centre Zone</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>066ASW0016</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="n">
-        <v>13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>325</v>
-      </c>
-      <c r="U79" t="n">
-        <v>19</v>
-      </c>
-      <c r="V79" t="n">
-        <v>64.4453</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-97.6319</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0016</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>119 Zone</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>065INE0004</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Copper, Cobalt, Platinum, Palladium</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="n">
-        <v>13</v>
-      </c>
-      <c r="T80" t="n">
-        <v>325</v>
-      </c>
-      <c r="U80" t="n">
-        <v>19</v>
-      </c>
-      <c r="V80" t="n">
-        <v>62.8675</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-96.99420000000001</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0004</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>076ENE0001</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>13</v>
-      </c>
-      <c r="T81" t="n">
-        <v>325</v>
-      </c>
-      <c r="U81" t="n">
-        <v>19</v>
-      </c>
-      <c r="V81" t="n">
-        <v>65.6164</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-110.7828</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Pan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>076ENW0004</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I82" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="n">
-        <v>13</v>
-      </c>
-      <c r="T82" t="n">
-        <v>325</v>
-      </c>
-      <c r="U82" t="n">
-        <v>19</v>
-      </c>
-      <c r="V82" t="n">
-        <v>65.6617</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-111.2056</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0004</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Jon</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>076ENE0002</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="n">
-        <v>13</v>
-      </c>
-      <c r="T83" t="n">
-        <v>325</v>
-      </c>
-      <c r="U83" t="n">
-        <v>19</v>
-      </c>
-      <c r="V83" t="n">
-        <v>65.5814</v>
-      </c>
-      <c r="W83" t="n">
-        <v>-110.9686</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0002</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Hackett River</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>076FNE0001</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Zinc, Lead, Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="n">
-        <v>13</v>
-      </c>
-      <c r="T84" t="n">
-        <v>325</v>
-      </c>
-      <c r="U84" t="n">
-        <v>19</v>
-      </c>
-      <c r="V84" t="n">
-        <v>65.91719999999999</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-108.3631</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076FNE0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Gondor</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>076ENW0005</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Zinc, Silver, Copper, Lead, Gold</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="n">
-        <v>13</v>
-      </c>
-      <c r="T85" t="n">
-        <v>325</v>
-      </c>
-      <c r="U85" t="n">
-        <v>19</v>
-      </c>
-      <c r="V85" t="n">
-        <v>65.5628</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-111.7969</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0005</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Musk</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>076GSW0001</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Zinc, Lead, Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="n">
-        <v>13</v>
-      </c>
-      <c r="T86" t="n">
-        <v>325</v>
-      </c>
-      <c r="U86" t="n">
-        <v>19</v>
-      </c>
-      <c r="V86" t="n">
-        <v>65.3231</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-107.6208</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076GSW0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>YON</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>076JNW0005</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Uranium, Copper</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="n">
-        <v>13</v>
-      </c>
-      <c r="T87" t="n">
-        <v>325</v>
-      </c>
-      <c r="U87" t="n">
-        <v>19</v>
-      </c>
-      <c r="V87" t="n">
-        <v>66.58329999999999</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-107.4667</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076JNW0005</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>POMIE</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>076JSW0003</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Uranium, Copper</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I88" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="n">
-        <v>13</v>
-      </c>
-      <c r="T88" t="n">
-        <v>325</v>
-      </c>
-      <c r="U88" t="n">
-        <v>19</v>
-      </c>
-      <c r="V88" t="n">
-        <v>66.217</v>
-      </c>
-      <c r="W88" t="n">
-        <v>-107.0177</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076JSW0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Ulu</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>076LNE0023</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Gold, As, Bismuth, Zinc, Silver, Cd</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I89" t="b">
-        <v>1</v>
-      </c>
-      <c r="J89" t="b">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="n">
-        <v>13</v>
-      </c>
-      <c r="T89" t="n">
-        <v>325</v>
-      </c>
-      <c r="U89" t="n">
-        <v>19</v>
-      </c>
-      <c r="V89" t="n">
-        <v>66.9067</v>
-      </c>
-      <c r="W89" t="n">
-        <v>-110.9706</v>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076LNE0023</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Gumbo Lake Ilmenite</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>076LSW0008</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Titanium</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Titanium, Vanadium, Iron</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I90" t="b">
-        <v>1</v>
-      </c>
-      <c r="J90" t="b">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="n">
-        <v>13</v>
-      </c>
-      <c r="T90" t="n">
-        <v>325</v>
-      </c>
-      <c r="U90" t="n">
-        <v>19</v>
-      </c>
-      <c r="V90" t="n">
-        <v>66.3167</v>
-      </c>
-      <c r="W90" t="n">
-        <v>-111.1944</v>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076LSW0008</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>North Central Vein</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>076MNW0084</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I91" t="b">
-        <v>1</v>
-      </c>
-      <c r="J91" t="b">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="n">
-        <v>13</v>
-      </c>
-      <c r="T91" t="n">
-        <v>325</v>
-      </c>
-      <c r="U91" t="n">
-        <v>19</v>
-      </c>
-      <c r="V91" t="n">
-        <v>67.7175</v>
-      </c>
-      <c r="W91" t="n">
-        <v>-111.3711</v>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0084</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Fred Vein</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>076MNW0085</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I92" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="n">
-        <v>13</v>
-      </c>
-      <c r="T92" t="n">
-        <v>325</v>
-      </c>
-      <c r="U92" t="n">
-        <v>19</v>
-      </c>
-      <c r="V92" t="n">
-        <v>67.71810000000001</v>
-      </c>
-      <c r="W92" t="n">
-        <v>-111.3583</v>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0085</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>George Lake</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>076GNW0003</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I93" t="b">
-        <v>1</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="n">
-        <v>13</v>
-      </c>
-      <c r="T93" t="n">
-        <v>325</v>
-      </c>
-      <c r="U93" t="n">
-        <v>19</v>
-      </c>
-      <c r="V93" t="n">
-        <v>65.9258</v>
-      </c>
-      <c r="W93" t="n">
-        <v>-107.4764</v>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076GNW0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>High Lake AB Zone</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>076MSE0053</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I94" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" t="b">
-        <v>0</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="n">
-        <v>13</v>
-      </c>
-      <c r="T94" t="n">
-        <v>325</v>
-      </c>
-      <c r="U94" t="n">
-        <v>19</v>
-      </c>
-      <c r="V94" t="n">
-        <v>67.3814</v>
-      </c>
-      <c r="W94" t="n">
-        <v>-110.85</v>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0053</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>High Lake D Zone</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>076MSE0054</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Silver, Lead, Gold</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I95" t="b">
-        <v>1</v>
-      </c>
-      <c r="J95" t="b">
-        <v>0</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="n">
-        <v>13</v>
-      </c>
-      <c r="T95" t="n">
-        <v>325</v>
-      </c>
-      <c r="U95" t="n">
-        <v>19</v>
-      </c>
-      <c r="V95" t="n">
-        <v>67.3758</v>
-      </c>
-      <c r="W95" t="n">
-        <v>-110.8436</v>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0054</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Turner Lake Main Gold</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>076NSE0010</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I96" t="b">
-        <v>1</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="n">
-        <v>13</v>
-      </c>
-      <c r="T96" t="n">
-        <v>325</v>
-      </c>
-      <c r="U96" t="n">
-        <v>19</v>
-      </c>
-      <c r="V96" t="n">
-        <v>67.2169</v>
-      </c>
-      <c r="W96" t="n">
-        <v>-108.9403</v>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076NSE0010</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Pistol Lake</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>076NSE0006</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I97" t="b">
-        <v>1</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="n">
-        <v>13</v>
-      </c>
-      <c r="T97" t="n">
-        <v>325</v>
-      </c>
-      <c r="U97" t="n">
-        <v>19</v>
-      </c>
-      <c r="V97" t="n">
-        <v>67.04940000000001</v>
-      </c>
-      <c r="W97" t="n">
-        <v>-108.7861</v>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076NSE0006</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>076ONE0010</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I98" t="b">
-        <v>1</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="n">
-        <v>13</v>
-      </c>
-      <c r="T98" t="n">
-        <v>325</v>
-      </c>
-      <c r="U98" t="n">
-        <v>19</v>
-      </c>
-      <c r="V98" t="n">
-        <v>67.6494</v>
-      </c>
-      <c r="W98" t="n">
-        <v>-106.3881</v>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ONE0010</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Granite</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>077ASW0013</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I99" t="b">
-        <v>1</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="n">
-        <v>13</v>
-      </c>
-      <c r="T99" t="n">
-        <v>325</v>
-      </c>
-      <c r="U99" t="n">
-        <v>19</v>
-      </c>
-      <c r="V99" t="n">
-        <v>68.1708</v>
-      </c>
-      <c r="W99" t="n">
-        <v>-106.5208</v>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0013</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Hope Bay Noel</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>077ASW0015</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I100" t="b">
-        <v>1</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="n">
-        <v>13</v>
-      </c>
-      <c r="T100" t="n">
-        <v>325</v>
-      </c>
-      <c r="U100" t="n">
-        <v>19</v>
-      </c>
-      <c r="V100" t="n">
-        <v>68.1069</v>
-      </c>
-      <c r="W100" t="n">
-        <v>-106.7292</v>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0015</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Hope Bay Discovery</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>077ASW0016</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I101" t="b">
-        <v>1</v>
-      </c>
-      <c r="J101" t="b">
-        <v>0</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="n">
-        <v>13</v>
-      </c>
-      <c r="T101" t="n">
-        <v>325</v>
-      </c>
-      <c r="U101" t="n">
-        <v>19</v>
-      </c>
-      <c r="V101" t="n">
-        <v>68.1194</v>
-      </c>
-      <c r="W101" t="n">
-        <v>-106.7083</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0016</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Izok Lake</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>086HNE0087</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I102" t="b">
-        <v>1</v>
-      </c>
-      <c r="J102" t="b">
-        <v>0</v>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="n">
-        <v>13</v>
-      </c>
-      <c r="T102" t="n">
-        <v>325</v>
-      </c>
-      <c r="U102" t="n">
-        <v>19</v>
-      </c>
-      <c r="V102" t="n">
-        <v>65.6311</v>
-      </c>
-      <c r="W102" t="n">
-        <v>-112.7989</v>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086HNE0087</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Takijuq H-41</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>086ISE0001</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I103" t="b">
-        <v>1</v>
-      </c>
-      <c r="J103" t="b">
-        <v>0</v>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="n">
-        <v>13</v>
-      </c>
-      <c r="T103" t="n">
-        <v>325</v>
-      </c>
-      <c r="U103" t="n">
-        <v>19</v>
-      </c>
-      <c r="V103" t="n">
-        <v>66.0342</v>
-      </c>
-      <c r="W103" t="n">
-        <v>-112.7094</v>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Takijuq H-10</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>086ISE0002</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Zinc, Lead, Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I104" t="b">
-        <v>1</v>
-      </c>
-      <c r="J104" t="b">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="n">
-        <v>13</v>
-      </c>
-      <c r="T104" t="n">
-        <v>325</v>
-      </c>
-      <c r="U104" t="n">
-        <v>19</v>
-      </c>
-      <c r="V104" t="n">
-        <v>66.06</v>
-      </c>
-      <c r="W104" t="n">
-        <v>-112.7536</v>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0002</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>CARL 7</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>086NNW0070</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I105" t="b">
-        <v>1</v>
-      </c>
-      <c r="J105" t="b">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="n">
-        <v>13</v>
-      </c>
-      <c r="T105" t="n">
-        <v>325</v>
-      </c>
-      <c r="U105" t="n">
-        <v>19</v>
-      </c>
-      <c r="V105" t="n">
-        <v>67.7333</v>
-      </c>
-      <c r="W105" t="n">
-        <v>-117.5931</v>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NNW0070</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Coronation Northwest Zone</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>086NSE0014</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I106" t="b">
-        <v>1</v>
-      </c>
-      <c r="J106" t="b">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="n">
-        <v>13</v>
-      </c>
-      <c r="T106" t="n">
-        <v>325</v>
-      </c>
-      <c r="U106" t="n">
-        <v>19</v>
-      </c>
-      <c r="V106" t="n">
-        <v>67.3347</v>
-      </c>
-      <c r="W106" t="n">
-        <v>-116.45</v>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0014</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Dick No. 1</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>086NSE0120</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I107" t="b">
-        <v>1</v>
-      </c>
-      <c r="J107" t="b">
-        <v>0</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="n">
-        <v>13</v>
-      </c>
-      <c r="T107" t="n">
-        <v>325</v>
-      </c>
-      <c r="U107" t="n">
-        <v>19</v>
-      </c>
-      <c r="V107" t="n">
-        <v>67.3306</v>
-      </c>
-      <c r="W107" t="n">
-        <v>-116.0431</v>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0120</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Wreck Lake</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>086NSE0121</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Advanced Exploration</t>
-        </is>
-      </c>
-      <c r="I108" t="b">
-        <v>1</v>
-      </c>
-      <c r="J108" t="b">
-        <v>0</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="n">
-        <v>13</v>
-      </c>
-      <c r="T108" t="n">
-        <v>325</v>
-      </c>
-      <c r="U108" t="n">
-        <v>19</v>
-      </c>
-      <c r="V108" t="n">
-        <v>67.41</v>
-      </c>
-      <c r="W108" t="n">
-        <v>-116.4119</v>
-      </c>
-      <c r="X108" t="inlineStr">
         <is>
           <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0121</t>
         </is>

--- a/site/nu_leads.xlsx
+++ b/site/nu_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,10 +616,10 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
         <v>35</v>
@@ -688,10 +688,10 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>35</v>
@@ -714,25 +714,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>steve test</t>
+          <t>Lupin Mine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>016LSE0001</t>
+          <t>076ENW0017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Minor Past Producer Renewed Exploration</t>
+          <t>Past Producer Care and Maintnc</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -762,17 +766,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>62.2542</v>
+        <v>65.7647</v>
       </c>
       <c r="W4" t="n">
-        <v>-62.2542</v>
+        <v>-111.225</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=016LSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0017</t>
         </is>
       </c>
     </row>
@@ -782,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Polaris</t>
+          <t>Roberts Lake Silver</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>068HSE0003</t>
+          <t>077ASW0004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Silver, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -834,17 +838,17 @@
         <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="V5" t="n">
-        <v>75.3989</v>
+        <v>68.1833</v>
       </c>
       <c r="W5" t="n">
-        <v>-96.92529999999999</v>
+        <v>-106.5458</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=068HSE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0004</t>
         </is>
       </c>
     </row>
@@ -854,29 +858,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #4</t>
+          <t>North Rankin Nickel Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>037CNE0006</t>
+          <t>055KNE0083</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Nickel, Copper, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -906,17 +910,17 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="V6" t="n">
-        <v>69.67400000000001</v>
+        <v>62.8144</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.8459</v>
+        <v>-92.0779</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0006</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0083</t>
         </is>
       </c>
     </row>
@@ -926,29 +930,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mary River - No. 3a Deposit</t>
+          <t>Rankin Inlet Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>037GSW0009</t>
+          <t>055KNE0145</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Nickel, Copper, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -978,17 +982,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="V7" t="n">
-        <v>71.3188</v>
+        <v>62.8131</v>
       </c>
       <c r="W7" t="n">
-        <v>-79.08110000000001</v>
+        <v>-92.07769999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0009</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KNE0145</t>
         </is>
       </c>
     </row>
@@ -998,29 +1002,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #5</t>
+          <t>Nanisivik Mine - K-Baseline Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>037CNE0007</t>
+          <t>048CSE0007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1050,17 +1054,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V8" t="n">
-        <v>69.66670000000001</v>
+        <v>73.0414</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.875</v>
+        <v>-84.4092</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0007</t>
         </is>
       </c>
     </row>
@@ -1070,29 +1074,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #6</t>
+          <t>Nanisivik Mine - Ocean View Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>037CNE0008</t>
+          <t>048CSE0004</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1122,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V9" t="n">
-        <v>69.66589999999999</v>
+        <v>73.0463</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.82510000000001</v>
+        <v>-84.3865</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0008</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0004</t>
         </is>
       </c>
     </row>
@@ -1142,29 +1146,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #7</t>
+          <t>steve test</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>037CNE0009</t>
+          <t>016LSE0001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Minor Past Producer Renewed Exploration</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1194,17 +1194,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V10" t="n">
-        <v>69.67659999999999</v>
+        <v>62.2542</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.92449999999999</v>
+        <v>-62.2542</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0009</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=016LSE0001</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1214,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eqe Bay</t>
+          <t>Polaris</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>037CNE0010</t>
+          <t>068HSE0003</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1266,17 +1266,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V11" t="n">
-        <v>69.6733</v>
+        <v>75.3989</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.8056</v>
+        <v>-96.92529999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0010</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=068HSE0003</t>
         </is>
       </c>
     </row>
@@ -1286,29 +1286,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mary River - No. 1 Deposit</t>
+          <t>Nanisivik Mine - Area 14 Zone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>037GSW0002</t>
+          <t>048CSE0005</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1338,17 +1338,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>71.32380000000001</v>
+        <v>73.029</v>
       </c>
       <c r="W12" t="n">
-        <v>-79.24160000000001</v>
+        <v>-84.4113</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0005</t>
         </is>
       </c>
     </row>
@@ -1358,29 +1358,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mary River - No. 2 Deposit</t>
+          <t>Nanisivik Mine - Shale Hill Zone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>037GSW0007</t>
+          <t>048CSE0006</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1410,17 +1410,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V13" t="n">
-        <v>71.32250000000001</v>
+        <v>73.0478</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.1327</v>
+        <v>-84.4639</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0006</t>
         </is>
       </c>
     </row>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mary River - No. 3 Deposit</t>
+          <t>Nanisivik Mine - Main Ore Zone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>037GSW0008</t>
+          <t>048CSE0002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Silver, Cd, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Advanced Exploration</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1482,17 +1482,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>71.3168</v>
+        <v>73.041</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.12869999999999</v>
+        <v>-84.49469999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0008</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0002</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Borealis - 1</t>
+          <t>Eqe Bay Iron Zone #4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>047BSE0001</t>
+          <t>037CNE0006</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1557,14 +1557,14 @@
         <v>19</v>
       </c>
       <c r="V15" t="n">
-        <v>68.21850000000001</v>
+        <v>69.67400000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>-85.4945</v>
+        <v>-76.8459</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0006</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Area 'D'</t>
+          <t>Mary River - No. 3a Deposit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>047ASW0009</t>
+          <t>037GSW0009</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1629,14 +1629,14 @@
         <v>19</v>
       </c>
       <c r="V16" t="n">
-        <v>68.3702</v>
+        <v>71.3188</v>
       </c>
       <c r="W16" t="n">
-        <v>-82.97620000000001</v>
+        <v>-79.08110000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0009</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0009</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Area 'E'</t>
+          <t>Eqe Bay Iron Zone #5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>047ASW0007</t>
+          <t>037CNE0007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1701,14 +1701,14 @@
         <v>19</v>
       </c>
       <c r="V17" t="n">
-        <v>68.1631</v>
+        <v>69.66670000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>-83.38849999999999</v>
+        <v>-76.875</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0007</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Area 'B'</t>
+          <t>Eqe Bay Iron Zone #6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>047ASW0004</t>
+          <t>037CNE0008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1773,14 +1773,14 @@
         <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>68.46120000000001</v>
+        <v>69.66589999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>-82.7294</v>
+        <v>-76.82510000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0008</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Area 'A' / Adler</t>
+          <t>Eqe Bay Iron Zone #7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>047ASW0001</t>
+          <t>037CNE0009</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1845,14 +1845,14 @@
         <v>19</v>
       </c>
       <c r="V19" t="n">
-        <v>68.47150000000001</v>
+        <v>69.67659999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>-82.7221</v>
+        <v>-76.92449999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0009</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Borealis - 2</t>
+          <t>Eqe Bay</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>047BSE0002</t>
+          <t>037CNE0010</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1917,14 +1917,14 @@
         <v>19</v>
       </c>
       <c r="V20" t="n">
-        <v>68.2056</v>
+        <v>69.6733</v>
       </c>
       <c r="W20" t="n">
-        <v>-85.4928</v>
+        <v>-76.8056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0010</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Borealis - 5 Southern Zone</t>
+          <t>Mary River - No. 1 Deposit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>047BSE0027</t>
+          <t>037GSW0002</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1989,14 +1989,14 @@
         <v>19</v>
       </c>
       <c r="V21" t="n">
-        <v>68.3648</v>
+        <v>71.32380000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>-85.3108</v>
+        <v>-79.24160000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0027</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0002</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Borealis - 5 Northern Zone</t>
+          <t>Mary River - No. 2 Deposit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>047BSE0026</t>
+          <t>037GSW0007</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2061,14 +2061,14 @@
         <v>19</v>
       </c>
       <c r="V22" t="n">
-        <v>68.3794</v>
+        <v>71.32250000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>-85.26819999999999</v>
+        <v>-79.1327</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0026</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0007</t>
         </is>
       </c>
     </row>
@@ -2078,22 +2078,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Borealis - 3 East Limb</t>
+          <t>Mary River - No. 3 Deposit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>047BSE0025</t>
+          <t>037GSW0008</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Advanced Exploration</t>
@@ -2129,14 +2133,14 @@
         <v>19</v>
       </c>
       <c r="V23" t="n">
-        <v>68.18899999999999</v>
+        <v>71.3168</v>
       </c>
       <c r="W23" t="n">
-        <v>-85.4982</v>
+        <v>-79.12869999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0025</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0008</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2150,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Borealis - 1 North Extension</t>
+          <t>Borealis - 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>047BSE0024</t>
+          <t>047BSE0001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2201,14 +2205,14 @@
         <v>19</v>
       </c>
       <c r="V24" t="n">
-        <v>68.2272</v>
+        <v>68.21850000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>-85.4879</v>
+        <v>-85.4945</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0024</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0001</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2222,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Borealis - 5 Central Zone</t>
+          <t>Area 'D'</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>047BSE0005</t>
+          <t>047ASW0009</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2273,14 +2277,14 @@
         <v>19</v>
       </c>
       <c r="V25" t="n">
-        <v>68.37090000000001</v>
+        <v>68.3702</v>
       </c>
       <c r="W25" t="n">
-        <v>-85.28060000000001</v>
+        <v>-82.97620000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0005</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0009</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2294,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Borealis - 4</t>
+          <t>Area 'C'</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>047BSE0004</t>
+          <t>047ASW0008</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2345,14 +2349,14 @@
         <v>19</v>
       </c>
       <c r="V26" t="n">
-        <v>68.2987</v>
+        <v>68.4328</v>
       </c>
       <c r="W26" t="n">
-        <v>-85.28279999999999</v>
+        <v>-82.78619999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0008</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2366,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Borealis - 3 West Limb</t>
+          <t>Area 'E'</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>047BSE0003</t>
+          <t>047ASW0007</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2417,14 +2421,14 @@
         <v>19</v>
       </c>
       <c r="V27" t="n">
-        <v>68.1915</v>
+        <v>68.1631</v>
       </c>
       <c r="W27" t="n">
-        <v>-85.50920000000001</v>
+        <v>-83.38849999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0007</t>
         </is>
       </c>
     </row>
@@ -2434,24 +2438,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Turquetil Lake Northwest</t>
+          <t>Area 'B'</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>055ENW0007</t>
+          <t>047ASW0004</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2480,23 +2484,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>19</v>
       </c>
       <c r="V28" t="n">
-        <v>61.98</v>
+        <v>68.46120000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>-95.9267</v>
+        <v>-82.7294</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055ENW0007</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0004</t>
         </is>
       </c>
     </row>
@@ -2506,24 +2510,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fat Lake</t>
+          <t>Area 'A' / Adler</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>055KSW0041</t>
+          <t>047ASW0001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, As, Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2561,14 +2565,14 @@
         <v>19</v>
       </c>
       <c r="V29" t="n">
-        <v>62.1201</v>
+        <v>68.47150000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>-93.8631</v>
+        <v>-82.7221</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KSW0041</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047ASW0001</t>
         </is>
       </c>
     </row>
@@ -2578,24 +2582,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cache Zone</t>
+          <t>Mary River - No. 4 Deposit</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>055LSE0045</t>
+          <t>037GSW0010</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2624,23 +2628,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>19</v>
       </c>
       <c r="V30" t="n">
-        <v>62.3675</v>
+        <v>71.4611</v>
       </c>
       <c r="W30" t="n">
-        <v>-94.6288</v>
+        <v>-79.8638</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0045</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037GSW0010</t>
         </is>
       </c>
     </row>
@@ -2650,24 +2654,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Borealis - 2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>055LSE0254</t>
+          <t>047BSE0002</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Uranium, fluorspar</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2705,14 +2709,14 @@
         <v>19</v>
       </c>
       <c r="V31" t="n">
-        <v>62.3253</v>
+        <v>68.2056</v>
       </c>
       <c r="W31" t="n">
-        <v>-94.65009999999999</v>
+        <v>-85.4928</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0254</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0002</t>
         </is>
       </c>
     </row>
@@ -2722,24 +2726,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spi Lake</t>
+          <t>Borealis - 5 Southern Zone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>055LSW0133</t>
+          <t>047BSE0027</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Gold, Lead</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2777,14 +2781,14 @@
         <v>19</v>
       </c>
       <c r="V32" t="n">
-        <v>62.0699</v>
+        <v>68.3648</v>
       </c>
       <c r="W32" t="n">
-        <v>-95.8784</v>
+        <v>-85.3108</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSW0133</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0027</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2798,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Maltby Lake Iron Deposit</t>
+          <t>Borealis - 5 Northern Zone</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>036CNW0001</t>
+          <t>047BSE0026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2849,14 +2853,14 @@
         <v>19</v>
       </c>
       <c r="V33" t="n">
-        <v>64.91670000000001</v>
+        <v>68.3794</v>
       </c>
       <c r="W33" t="n">
-        <v>-77.9333</v>
+        <v>-85.26819999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=036CNW0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0026</t>
         </is>
       </c>
     </row>
@@ -2866,26 +2870,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #1</t>
+          <t>Borealis - 3 East Limb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>037CNE0001</t>
+          <t>047BSE0025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Advanced Exploration</t>
@@ -2921,14 +2921,14 @@
         <v>19</v>
       </c>
       <c r="V34" t="n">
-        <v>69.68989999999999</v>
+        <v>68.18899999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.7471</v>
+        <v>-85.4982</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0025</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #1A</t>
+          <t>Borealis - 1 North Extension</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>037CNE0002</t>
+          <t>047BSE0024</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2993,14 +2993,14 @@
         <v>19</v>
       </c>
       <c r="V35" t="n">
-        <v>69.71120000000001</v>
+        <v>68.2272</v>
       </c>
       <c r="W35" t="n">
-        <v>-76.6835</v>
+        <v>-85.4879</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0024</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #2</t>
+          <t>Borealis - 5 Central Zone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>037CNE0003</t>
+          <t>047BSE0005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3065,14 +3065,14 @@
         <v>19</v>
       </c>
       <c r="V36" t="n">
-        <v>69.6797</v>
+        <v>68.37090000000001</v>
       </c>
       <c r="W36" t="n">
-        <v>-76.8171</v>
+        <v>-85.28060000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0005</t>
         </is>
       </c>
     </row>
@@ -3082,24 +3082,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eqe Bay Iron Zone #3</t>
+          <t>Nanisivik Mines - North Pyrite Zone</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>037CNE0004</t>
+          <t>048CSE0012</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3137,14 +3137,14 @@
         <v>19</v>
       </c>
       <c r="V37" t="n">
-        <v>69.6778</v>
+        <v>73.05370000000001</v>
       </c>
       <c r="W37" t="n">
-        <v>-76.8</v>
+        <v>-84.4376</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=048CSE0012</t>
         </is>
       </c>
     </row>
@@ -3154,24 +3154,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rochon Lake</t>
+          <t>Borealis - 4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>065CNW0012</t>
+          <t>047BSE0004</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3209,14 +3209,14 @@
         <v>19</v>
       </c>
       <c r="V38" t="n">
-        <v>60.8211</v>
+        <v>68.2987</v>
       </c>
       <c r="W38" t="n">
-        <v>-101.9109</v>
+        <v>-85.28279999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065CNW0012</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0004</t>
         </is>
       </c>
     </row>
@@ -3226,24 +3226,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Borealis - 3 West Limb</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>058CSW0004</t>
+          <t>047BSE0003</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Diam</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3281,14 +3281,14 @@
         <v>19</v>
       </c>
       <c r="V39" t="n">
-        <v>73.4628</v>
+        <v>68.1915</v>
       </c>
       <c r="W39" t="n">
-        <v>-92.3297</v>
+        <v>-85.50920000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0004</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=047BSE0003</t>
         </is>
       </c>
     </row>
@@ -3298,24 +3298,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Batty</t>
+          <t>Turquetil Lake Main Zone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>058CSW0003</t>
+          <t>055ENW0008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Diam</t>
+          <t>Gold, As, Copper, Zinc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3353,14 +3353,14 @@
         <v>19</v>
       </c>
       <c r="V40" t="n">
-        <v>73.34690000000001</v>
+        <v>61.9718</v>
       </c>
       <c r="W40" t="n">
-        <v>-92.015</v>
+        <v>-95.94070000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0003</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055ENW0008</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lowo Lake</t>
+          <t>Turquetil Lake Northwest</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>065HSW0013</t>
+          <t>055ENW0007</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, As</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3425,14 +3425,14 @@
         <v>19</v>
       </c>
       <c r="V41" t="n">
-        <v>61.0527</v>
+        <v>61.98</v>
       </c>
       <c r="W41" t="n">
-        <v>-97.8574</v>
+        <v>-95.9267</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HSW0013</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055ENW0007</t>
         </is>
       </c>
     </row>
@@ -3442,24 +3442,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Outlet Bay</t>
+          <t>Meliadine East</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>065NSE0001</t>
+          <t>055JNW0001</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold, As, Copper</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3497,14 +3497,14 @@
         <v>19</v>
       </c>
       <c r="V42" t="n">
-        <v>63.3503</v>
+        <v>62.9602</v>
       </c>
       <c r="W42" t="n">
-        <v>-100.5005</v>
+        <v>-91.9315</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065NSE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055JNW0001</t>
         </is>
       </c>
     </row>
@@ -3514,24 +3514,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kiggavik East Zone</t>
+          <t>Fat Lake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>066ASW0017</t>
+          <t>055KSW0041</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold, Copper, Lead, As, Zinc</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3560,23 +3560,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
         <v>19</v>
       </c>
       <c r="V43" t="n">
-        <v>64.4461</v>
+        <v>62.1201</v>
       </c>
       <c r="W43" t="n">
-        <v>-97.6181</v>
+        <v>-93.8631</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0017</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055KSW0041</t>
         </is>
       </c>
     </row>
@@ -3586,24 +3586,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bong Grid</t>
+          <t>Cache Zone</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>066ASW0018</t>
+          <t>055LSE0045</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3641,14 +3641,14 @@
         <v>19</v>
       </c>
       <c r="V44" t="n">
-        <v>64.4158</v>
+        <v>62.3675</v>
       </c>
       <c r="W44" t="n">
-        <v>-97.70310000000001</v>
+        <v>-94.6288</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0018</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0045</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sleek Grid</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>066ASW0020</t>
+          <t>055LSE0254</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Uranium, fluorspar</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3704,23 +3704,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U45" t="n">
         <v>19</v>
       </c>
       <c r="V45" t="n">
-        <v>64.36279999999999</v>
+        <v>62.3253</v>
       </c>
       <c r="W45" t="n">
-        <v>-97.8369</v>
+        <v>-94.65009999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0020</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSE0254</t>
         </is>
       </c>
     </row>
@@ -3730,24 +3730,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Granite Grid</t>
+          <t>Spi Lake</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>066ASW0019</t>
+          <t>055LSW0133</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Copper, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3776,23 +3776,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T46" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U46" t="n">
         <v>19</v>
       </c>
       <c r="V46" t="n">
-        <v>64.4297</v>
+        <v>62.0699</v>
       </c>
       <c r="W46" t="n">
-        <v>-97.7792</v>
+        <v>-95.8784</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0019</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055LSW0133</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Andrew Lake Deposit</t>
+          <t>Shane Lake Project - Ms Claims</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>066ASW0022</t>
+          <t>055MNW0038</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3857,14 +3857,14 @@
         <v>19</v>
       </c>
       <c r="V47" t="n">
-        <v>64.3344</v>
+        <v>63.8337</v>
       </c>
       <c r="W47" t="n">
-        <v>-97.8961</v>
+        <v>-95.0335</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0022</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055MNW0038</t>
         </is>
       </c>
     </row>
@@ -3874,24 +3874,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>End Grid</t>
+          <t>Meliadine West</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>066ASW0021</t>
+          <t>055NSE0001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold, As, Lead</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3929,14 +3929,14 @@
         <v>19</v>
       </c>
       <c r="V48" t="n">
-        <v>64.3456</v>
+        <v>63.0226</v>
       </c>
       <c r="W48" t="n">
-        <v>-97.86499999999999</v>
+        <v>-92.20569999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0021</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055NSE0001</t>
         </is>
       </c>
     </row>
@@ -3946,12 +3946,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vault</t>
+          <t>Wolf Main</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>066HSE0012</t>
+          <t>055NSE0003</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold, Copper, As, Zinc, Lead</t>
+          <t>Gold, As, Lead</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4001,14 +4001,14 @@
         <v>19</v>
       </c>
       <c r="V49" t="n">
-        <v>65.0763</v>
+        <v>63.0303</v>
       </c>
       <c r="W49" t="n">
-        <v>-96.0031</v>
+        <v>-92.29989999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0012</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055NSE0003</t>
         </is>
       </c>
     </row>
@@ -4018,24 +4018,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Third Portage</t>
+          <t>Maltby Lake Iron Deposit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>066HSE0015</t>
+          <t>036CNW0001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gold, Copper, As</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4073,14 +4073,14 @@
         <v>19</v>
       </c>
       <c r="V50" t="n">
-        <v>65.01739999999999</v>
+        <v>64.91670000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>-96.04810000000001</v>
+        <v>-77.9333</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0015</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=036CNW0001</t>
         </is>
       </c>
     </row>
@@ -4090,24 +4090,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Goose Island</t>
+          <t>Eqe Bay Iron Zone #1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>066HSE0017</t>
+          <t>037CNE0001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gold, Copper, As</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4145,14 +4145,14 @@
         <v>19</v>
       </c>
       <c r="V51" t="n">
-        <v>65.0057</v>
+        <v>69.68989999999999</v>
       </c>
       <c r="W51" t="n">
-        <v>-96.0556</v>
+        <v>-76.7471</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0017</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0001</t>
         </is>
       </c>
     </row>
@@ -4162,24 +4162,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>North Portage</t>
+          <t>Eqe Bay Iron Zone #1A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>066HSE0016</t>
+          <t>037CNE0002</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gold, Copper, As</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4217,14 +4217,14 @@
         <v>19</v>
       </c>
       <c r="V52" t="n">
-        <v>65.0273</v>
+        <v>69.71120000000001</v>
       </c>
       <c r="W52" t="n">
-        <v>-96.0487</v>
+        <v>-76.6835</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0016</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0002</t>
         </is>
       </c>
     </row>
@@ -4234,24 +4234,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>Eqe Bay Iron Zone #2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>066HSE0023</t>
+          <t>037CNE0003</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold, As, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4280,23 +4280,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>19</v>
       </c>
       <c r="V53" t="n">
-        <v>65.15219999999999</v>
+        <v>69.6797</v>
       </c>
       <c r="W53" t="n">
-        <v>-96.0887</v>
+        <v>-76.8171</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0023</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0003</t>
         </is>
       </c>
     </row>
@@ -4306,24 +4306,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bay Zone</t>
+          <t>Eqe Bay Iron Zone #3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>066HSE0024</t>
+          <t>037CNE0004</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold, Copper, As</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4361,14 +4361,14 @@
         <v>19</v>
       </c>
       <c r="V54" t="n">
-        <v>65.01479999999999</v>
+        <v>69.6778</v>
       </c>
       <c r="W54" t="n">
-        <v>-96.0534</v>
+        <v>-76.8</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0024</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=037CNE0004</t>
         </is>
       </c>
     </row>
@@ -4378,24 +4378,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kiggavik Centre Zone</t>
+          <t>Rochon Lake</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>066ASW0016</t>
+          <t>065CNW0012</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4424,23 +4424,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T55" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U55" t="n">
         <v>19</v>
       </c>
       <c r="V55" t="n">
-        <v>64.4453</v>
+        <v>60.8211</v>
       </c>
       <c r="W55" t="n">
-        <v>-97.6319</v>
+        <v>-101.9109</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0016</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065CNW0012</t>
         </is>
       </c>
     </row>
@@ -4450,24 +4450,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>076ENE0001</t>
+          <t>058CSW0004</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diam</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4505,14 +4505,14 @@
         <v>19</v>
       </c>
       <c r="V56" t="n">
-        <v>65.6164</v>
+        <v>73.4628</v>
       </c>
       <c r="W56" t="n">
-        <v>-110.7828</v>
+        <v>-92.3297</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0004</t>
         </is>
       </c>
     </row>
@@ -4522,24 +4522,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cannu Zone</t>
+          <t>Batty</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>066HSE0035</t>
+          <t>058CSW0003</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Copper, As</t>
+          <t>Diam</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4577,14 +4577,14 @@
         <v>19</v>
       </c>
       <c r="V57" t="n">
-        <v>65.0324</v>
+        <v>73.34690000000001</v>
       </c>
       <c r="W57" t="n">
-        <v>-96.0479</v>
+        <v>-92.015</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0035</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=058CSW0003</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jon</t>
+          <t>Three Bluffs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>076ENE0002</t>
+          <t>056JNW0007</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, As, Copper</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4649,14 +4649,14 @@
         <v>19</v>
       </c>
       <c r="V58" t="n">
-        <v>65.5814</v>
+        <v>66.6497</v>
       </c>
       <c r="W58" t="n">
-        <v>-110.9686</v>
+        <v>-91.4093</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=056JNW0007</t>
         </is>
       </c>
     </row>
@@ -4666,24 +4666,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jericho North</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>076ENW0031</t>
+          <t>055NSE0004</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>Gold, As</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4712,23 +4712,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T59" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U59" t="n">
         <v>19</v>
       </c>
       <c r="V59" t="n">
-        <v>65.9992</v>
+        <v>63.009</v>
       </c>
       <c r="W59" t="n">
-        <v>-111.4777</v>
+        <v>-92.2201</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0031</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=055NSE0004</t>
         </is>
       </c>
     </row>
@@ -4738,24 +4738,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hackett River</t>
+          <t>Ferguson Lake</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>076FNE0001</t>
+          <t>065INE0001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Silver, Gold</t>
+          <t>Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4793,14 +4793,14 @@
         <v>19</v>
       </c>
       <c r="V60" t="n">
-        <v>65.91719999999999</v>
+        <v>62.8733</v>
       </c>
       <c r="W60" t="n">
-        <v>-108.3631</v>
+        <v>-96.8331</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076FNE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0001</t>
         </is>
       </c>
     </row>
@@ -4810,24 +4810,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gondor</t>
+          <t>Lowo Lake</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>076ENW0005</t>
+          <t>065HSW0013</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold</t>
+          <t>Gold, As</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4865,14 +4865,14 @@
         <v>19</v>
       </c>
       <c r="V61" t="n">
-        <v>65.5628</v>
+        <v>61.0527</v>
       </c>
       <c r="W61" t="n">
-        <v>-111.7969</v>
+        <v>-97.8574</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0005</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HSW0013</t>
         </is>
       </c>
     </row>
@@ -4882,12 +4882,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Musk</t>
+          <t>Heninga Lake - Eastern Zone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>076GSW0001</t>
+          <t>065HNE0023</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Silver, Gold</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4937,14 +4937,14 @@
         <v>19</v>
       </c>
       <c r="V62" t="n">
-        <v>65.3231</v>
+        <v>61.7756</v>
       </c>
       <c r="W62" t="n">
-        <v>-107.6208</v>
+        <v>-96.1996</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076GSW0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HNE0023</t>
         </is>
       </c>
     </row>
@@ -4954,24 +4954,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gumbo Lake Ilmenite</t>
+          <t>M Zone</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>076LSW0008</t>
+          <t>065INE0005</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Iron</t>
+          <t>Copper, Cobalt, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5009,14 +5009,14 @@
         <v>19</v>
       </c>
       <c r="V63" t="n">
-        <v>66.3167</v>
+        <v>62.8742</v>
       </c>
       <c r="W63" t="n">
-        <v>-111.1944</v>
+        <v>-96.80110000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076LSW0008</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0005</t>
         </is>
       </c>
     </row>
@@ -5026,26 +5026,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>North Central Vein</t>
+          <t>M Zone</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>076MNW0084</t>
+          <t>065ISE0011</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Advanced Exploration</t>
@@ -5081,14 +5077,14 @@
         <v>19</v>
       </c>
       <c r="V64" t="n">
-        <v>67.7175</v>
+        <v>62.8742</v>
       </c>
       <c r="W64" t="n">
-        <v>-111.3711</v>
+        <v>-96.78440000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0084</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065ISE0011</t>
         </is>
       </c>
     </row>
@@ -5098,24 +5094,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fred Vein</t>
+          <t>Nip, Rev (noranda Expln.)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>076MNW0085</t>
+          <t>065JNE0019</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium, Copper, Silver, Lead</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5153,14 +5149,14 @@
         <v>19</v>
       </c>
       <c r="V65" t="n">
-        <v>67.71810000000001</v>
+        <v>62.5303</v>
       </c>
       <c r="W65" t="n">
-        <v>-111.3583</v>
+        <v>-98.7829</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0085</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065JNE0019</t>
         </is>
       </c>
     </row>
@@ -5170,24 +5166,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>High Lake AB Zone</t>
+          <t>Rib &amp; Fst (Noranda Expln.)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>076MSE0053</t>
+          <t>065JNW0006</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5216,23 +5212,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>19</v>
       </c>
       <c r="V66" t="n">
-        <v>67.3814</v>
+        <v>62.5331</v>
       </c>
       <c r="W66" t="n">
-        <v>-110.85</v>
+        <v>-99.0907</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0053</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065JNW0006</t>
         </is>
       </c>
     </row>
@@ -5242,24 +5238,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>High Lake D Zone</t>
+          <t>Outlet Bay</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>076MSE0054</t>
+          <t>065NSE0001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Lead, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5288,23 +5284,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
         <v>19</v>
       </c>
       <c r="V67" t="n">
-        <v>67.3758</v>
+        <v>63.3503</v>
       </c>
       <c r="W67" t="n">
-        <v>-110.8436</v>
+        <v>-100.5005</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0054</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065NSE0001</t>
         </is>
       </c>
     </row>
@@ -5314,24 +5310,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Izok Lake</t>
+          <t>Nutarawit Lake</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>086HNE0087</t>
+          <t>065OSE0003</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5369,14 +5365,14 @@
         <v>19</v>
       </c>
       <c r="V68" t="n">
-        <v>65.6311</v>
+        <v>63.0786</v>
       </c>
       <c r="W68" t="n">
-        <v>-112.7989</v>
+        <v>-98.352</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086HNE0087</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065OSE0003</t>
         </is>
       </c>
     </row>
@@ -5386,24 +5382,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Takijuq H-41</t>
+          <t>Ferguson Lake</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>086ISE0001</t>
+          <t>065INE0002</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Copper, Nickel, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5441,14 +5437,14 @@
         <v>19</v>
       </c>
       <c r="V69" t="n">
-        <v>66.0342</v>
+        <v>62.8667</v>
       </c>
       <c r="W69" t="n">
-        <v>-112.7094</v>
+        <v>-96.8417</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0001</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0002</t>
         </is>
       </c>
     </row>
@@ -5458,24 +5454,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Takijuq H-10</t>
+          <t>Heninga Lake - West Zone</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>086ISE0002</t>
+          <t>065HNE0042</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Silver, Gold</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5513,14 +5509,14 @@
         <v>19</v>
       </c>
       <c r="V70" t="n">
-        <v>66.06</v>
+        <v>61.7733</v>
       </c>
       <c r="W70" t="n">
-        <v>-112.7536</v>
+        <v>-96.21129999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0002</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065HNE0042</t>
         </is>
       </c>
     </row>
@@ -5530,24 +5526,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Coronation Northwest Zone</t>
+          <t>Kiggavik East Zone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>086NSE0014</t>
+          <t>066ASW0017</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5585,14 +5581,14 @@
         <v>19</v>
       </c>
       <c r="V71" t="n">
-        <v>67.3347</v>
+        <v>64.4461</v>
       </c>
       <c r="W71" t="n">
-        <v>-116.45</v>
+        <v>-97.6181</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0014</t>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0017</t>
         </is>
       </c>
     </row>
@@ -5602,24 +5598,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wreck Lake</t>
+          <t>Bong Grid</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>086NSE0121</t>
+          <t>066ASW0018</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5657,12 +5653,2604 @@
         <v>19</v>
       </c>
       <c r="V72" t="n">
+        <v>64.4158</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-97.70310000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sleek Grid</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>066ASW0020</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>13</v>
+      </c>
+      <c r="T73" t="n">
+        <v>325</v>
+      </c>
+      <c r="U73" t="n">
+        <v>19</v>
+      </c>
+      <c r="V73" t="n">
+        <v>64.36279999999999</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-97.8369</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0020</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Granite Grid</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>066ASW0019</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>13</v>
+      </c>
+      <c r="T74" t="n">
+        <v>325</v>
+      </c>
+      <c r="U74" t="n">
+        <v>19</v>
+      </c>
+      <c r="V74" t="n">
+        <v>64.4297</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-97.7792</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0019</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Andrew Lake Deposit</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>066ASW0022</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>13</v>
+      </c>
+      <c r="T75" t="n">
+        <v>325</v>
+      </c>
+      <c r="U75" t="n">
+        <v>19</v>
+      </c>
+      <c r="V75" t="n">
+        <v>64.3344</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-97.8961</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0022</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Naujatuuk Lake</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>066GSE0002</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Uranium, Iron</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>13</v>
+      </c>
+      <c r="T76" t="n">
+        <v>325</v>
+      </c>
+      <c r="U76" t="n">
+        <v>19</v>
+      </c>
+      <c r="V76" t="n">
+        <v>65.2004</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-98.9171</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066GSE0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>End Grid</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>066ASW0021</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>325</v>
+      </c>
+      <c r="U77" t="n">
+        <v>19</v>
+      </c>
+      <c r="V77" t="n">
+        <v>64.3456</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-97.86499999999999</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0021</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>066HSE0023</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Gold, As, Copper</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>325</v>
+      </c>
+      <c r="U78" t="n">
+        <v>19</v>
+      </c>
+      <c r="V78" t="n">
+        <v>65.15219999999999</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-96.0887</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066HSE0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kiggavik Centre Zone</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>066ASW0016</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>325</v>
+      </c>
+      <c r="U79" t="n">
+        <v>19</v>
+      </c>
+      <c r="V79" t="n">
+        <v>64.4453</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-97.6319</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=066ASW0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>119 Zone</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>065INE0004</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Copper, Cobalt, Platinum, Palladium</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>13</v>
+      </c>
+      <c r="T80" t="n">
+        <v>325</v>
+      </c>
+      <c r="U80" t="n">
+        <v>19</v>
+      </c>
+      <c r="V80" t="n">
+        <v>62.8675</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-96.99420000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=065INE0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>076ENE0001</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>13</v>
+      </c>
+      <c r="T81" t="n">
+        <v>325</v>
+      </c>
+      <c r="U81" t="n">
+        <v>19</v>
+      </c>
+      <c r="V81" t="n">
+        <v>65.6164</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-110.7828</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>076ENW0004</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>13</v>
+      </c>
+      <c r="T82" t="n">
+        <v>325</v>
+      </c>
+      <c r="U82" t="n">
+        <v>19</v>
+      </c>
+      <c r="V82" t="n">
+        <v>65.6617</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-111.2056</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>076ENE0002</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>13</v>
+      </c>
+      <c r="T83" t="n">
+        <v>325</v>
+      </c>
+      <c r="U83" t="n">
+        <v>19</v>
+      </c>
+      <c r="V83" t="n">
+        <v>65.5814</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-110.9686</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENE0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Hackett River</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>076FNE0001</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>325</v>
+      </c>
+      <c r="U84" t="n">
+        <v>19</v>
+      </c>
+      <c r="V84" t="n">
+        <v>65.91719999999999</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-108.3631</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076FNE0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Gondor</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>076ENW0005</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Zinc, Silver, Copper, Lead, Gold</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>13</v>
+      </c>
+      <c r="T85" t="n">
+        <v>325</v>
+      </c>
+      <c r="U85" t="n">
+        <v>19</v>
+      </c>
+      <c r="V85" t="n">
+        <v>65.5628</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-111.7969</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ENW0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Musk</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>076GSW0001</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>13</v>
+      </c>
+      <c r="T86" t="n">
+        <v>325</v>
+      </c>
+      <c r="U86" t="n">
+        <v>19</v>
+      </c>
+      <c r="V86" t="n">
+        <v>65.3231</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-107.6208</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076GSW0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>YON</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>076JNW0005</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Uranium, Copper</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>13</v>
+      </c>
+      <c r="T87" t="n">
+        <v>325</v>
+      </c>
+      <c r="U87" t="n">
+        <v>19</v>
+      </c>
+      <c r="V87" t="n">
+        <v>66.58329999999999</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-107.4667</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076JNW0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>POMIE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>076JSW0003</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Uranium, Copper</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>13</v>
+      </c>
+      <c r="T88" t="n">
+        <v>325</v>
+      </c>
+      <c r="U88" t="n">
+        <v>19</v>
+      </c>
+      <c r="V88" t="n">
+        <v>66.217</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-107.0177</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076JSW0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ulu</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>076LNE0023</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Gold, As, Bismuth, Zinc, Silver, Cd</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>13</v>
+      </c>
+      <c r="T89" t="n">
+        <v>325</v>
+      </c>
+      <c r="U89" t="n">
+        <v>19</v>
+      </c>
+      <c r="V89" t="n">
+        <v>66.9067</v>
+      </c>
+      <c r="W89" t="n">
+        <v>-110.9706</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076LNE0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Gumbo Lake Ilmenite</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>076LSW0008</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Titanium</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Titanium, Vanadium, Iron</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>13</v>
+      </c>
+      <c r="T90" t="n">
+        <v>325</v>
+      </c>
+      <c r="U90" t="n">
+        <v>19</v>
+      </c>
+      <c r="V90" t="n">
+        <v>66.3167</v>
+      </c>
+      <c r="W90" t="n">
+        <v>-111.1944</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076LSW0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>North Central Vein</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>076MNW0084</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>13</v>
+      </c>
+      <c r="T91" t="n">
+        <v>325</v>
+      </c>
+      <c r="U91" t="n">
+        <v>19</v>
+      </c>
+      <c r="V91" t="n">
+        <v>67.7175</v>
+      </c>
+      <c r="W91" t="n">
+        <v>-111.3711</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0084</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fred Vein</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>076MNW0085</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>13</v>
+      </c>
+      <c r="T92" t="n">
+        <v>325</v>
+      </c>
+      <c r="U92" t="n">
+        <v>19</v>
+      </c>
+      <c r="V92" t="n">
+        <v>67.71810000000001</v>
+      </c>
+      <c r="W92" t="n">
+        <v>-111.3583</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MNW0085</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>George Lake</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>076GNW0003</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>13</v>
+      </c>
+      <c r="T93" t="n">
+        <v>325</v>
+      </c>
+      <c r="U93" t="n">
+        <v>19</v>
+      </c>
+      <c r="V93" t="n">
+        <v>65.9258</v>
+      </c>
+      <c r="W93" t="n">
+        <v>-107.4764</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076GNW0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>High Lake AB Zone</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>076MSE0053</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>13</v>
+      </c>
+      <c r="T94" t="n">
+        <v>325</v>
+      </c>
+      <c r="U94" t="n">
+        <v>19</v>
+      </c>
+      <c r="V94" t="n">
+        <v>67.3814</v>
+      </c>
+      <c r="W94" t="n">
+        <v>-110.85</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0053</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>High Lake D Zone</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>076MSE0054</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Silver, Lead, Gold</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>13</v>
+      </c>
+      <c r="T95" t="n">
+        <v>325</v>
+      </c>
+      <c r="U95" t="n">
+        <v>19</v>
+      </c>
+      <c r="V95" t="n">
+        <v>67.3758</v>
+      </c>
+      <c r="W95" t="n">
+        <v>-110.8436</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076MSE0054</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Turner Lake Main Gold</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>076NSE0010</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>13</v>
+      </c>
+      <c r="T96" t="n">
+        <v>325</v>
+      </c>
+      <c r="U96" t="n">
+        <v>19</v>
+      </c>
+      <c r="V96" t="n">
+        <v>67.2169</v>
+      </c>
+      <c r="W96" t="n">
+        <v>-108.9403</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076NSE0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pistol Lake</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>076NSE0006</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>13</v>
+      </c>
+      <c r="T97" t="n">
+        <v>325</v>
+      </c>
+      <c r="U97" t="n">
+        <v>19</v>
+      </c>
+      <c r="V97" t="n">
+        <v>67.04940000000001</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-108.7861</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076NSE0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>076ONE0010</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>13</v>
+      </c>
+      <c r="T98" t="n">
+        <v>325</v>
+      </c>
+      <c r="U98" t="n">
+        <v>19</v>
+      </c>
+      <c r="V98" t="n">
+        <v>67.6494</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-106.3881</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=076ONE0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Granite</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>077ASW0013</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I99" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>13</v>
+      </c>
+      <c r="T99" t="n">
+        <v>325</v>
+      </c>
+      <c r="U99" t="n">
+        <v>19</v>
+      </c>
+      <c r="V99" t="n">
+        <v>68.1708</v>
+      </c>
+      <c r="W99" t="n">
+        <v>-106.5208</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hope Bay Noel</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>077ASW0015</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>13</v>
+      </c>
+      <c r="T100" t="n">
+        <v>325</v>
+      </c>
+      <c r="U100" t="n">
+        <v>19</v>
+      </c>
+      <c r="V100" t="n">
+        <v>68.1069</v>
+      </c>
+      <c r="W100" t="n">
+        <v>-106.7292</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0015</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hope Bay Discovery</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>077ASW0016</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I101" t="b">
+        <v>1</v>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>13</v>
+      </c>
+      <c r="T101" t="n">
+        <v>325</v>
+      </c>
+      <c r="U101" t="n">
+        <v>19</v>
+      </c>
+      <c r="V101" t="n">
+        <v>68.1194</v>
+      </c>
+      <c r="W101" t="n">
+        <v>-106.7083</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=077ASW0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Izok Lake</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>086HNE0087</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I102" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>13</v>
+      </c>
+      <c r="T102" t="n">
+        <v>325</v>
+      </c>
+      <c r="U102" t="n">
+        <v>19</v>
+      </c>
+      <c r="V102" t="n">
+        <v>65.6311</v>
+      </c>
+      <c r="W102" t="n">
+        <v>-112.7989</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086HNE0087</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Takijuq H-41</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>086ISE0001</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I103" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>13</v>
+      </c>
+      <c r="T103" t="n">
+        <v>325</v>
+      </c>
+      <c r="U103" t="n">
+        <v>19</v>
+      </c>
+      <c r="V103" t="n">
+        <v>66.0342</v>
+      </c>
+      <c r="W103" t="n">
+        <v>-112.7094</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Takijuq H-10</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>086ISE0002</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Zinc, Lead, Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I104" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>13</v>
+      </c>
+      <c r="T104" t="n">
+        <v>325</v>
+      </c>
+      <c r="U104" t="n">
+        <v>19</v>
+      </c>
+      <c r="V104" t="n">
+        <v>66.06</v>
+      </c>
+      <c r="W104" t="n">
+        <v>-112.7536</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086ISE0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CARL 7</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>086NNW0070</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I105" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>13</v>
+      </c>
+      <c r="T105" t="n">
+        <v>325</v>
+      </c>
+      <c r="U105" t="n">
+        <v>19</v>
+      </c>
+      <c r="V105" t="n">
+        <v>67.7333</v>
+      </c>
+      <c r="W105" t="n">
+        <v>-117.5931</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NNW0070</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Coronation Northwest Zone</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>086NSE0014</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I106" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>13</v>
+      </c>
+      <c r="T106" t="n">
+        <v>325</v>
+      </c>
+      <c r="U106" t="n">
+        <v>19</v>
+      </c>
+      <c r="V106" t="n">
+        <v>67.3347</v>
+      </c>
+      <c r="W106" t="n">
+        <v>-116.45</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Dick No. 1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>086NSE0120</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I107" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>13</v>
+      </c>
+      <c r="T107" t="n">
+        <v>325</v>
+      </c>
+      <c r="U107" t="n">
+        <v>19</v>
+      </c>
+      <c r="V107" t="n">
+        <v>67.3306</v>
+      </c>
+      <c r="W107" t="n">
+        <v>-116.0431</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0120</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Wreck Lake</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>086NSE0121</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I108" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>13</v>
+      </c>
+      <c r="T108" t="n">
+        <v>325</v>
+      </c>
+      <c r="U108" t="n">
+        <v>19</v>
+      </c>
+      <c r="V108" t="n">
         <v>67.41</v>
       </c>
-      <c r="W72" t="n">
+      <c r="W108" t="n">
         <v>-116.4119</v>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>http://nunavutgeoscience.ca/apps/showing/showRprt.php?ia=1&amp;sId=086NSE0121</t>
         </is>
